--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_393_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_393_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,7 +1335,7 @@
         <v>20</v>
       </c>
       <c r="T17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>62:59</t>
+          <t>33:00</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>30.7%</t>
         </is>
       </c>
     </row>
@@ -1531,10 +1531,10 @@
         <v>17</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>52:23</t>
+          <t>32:24</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,22 +1647,22 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>44.8%</t>
         </is>
       </c>
     </row>
@@ -1730,13 +1730,13 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>6</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>61:50</t>
+          <t>31:51</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,22 +1843,22 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>5.7%</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -2315,16 +2315,16 @@
         <v>31</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>10</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>72:52</t>
+          <t>32:53</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,22 +2431,22 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2823,17 +2823,17 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>47:45</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AN26" t="n">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -3225,12 +3225,12 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
@@ -3494,13 +3494,13 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>4</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>52:26</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="AN28" t="n">
@@ -3607,22 +3607,22 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
     </row>
@@ -3827,16 +3827,16 @@
         <v>105</v>
       </c>
       <c r="T30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>29</v>
@@ -4292,7 +4292,7 @@
         <v>16</v>
       </c>
       <c r="T35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>57:25</t>
+          <t>27:25</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>33.5%</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>44:43</t>
+          <t>24:44</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4604,22 +4604,22 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.3%</t>
         </is>
       </c>
     </row>
@@ -4684,16 +4684,16 @@
         <v>13</v>
       </c>
       <c r="T37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>9</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>53:17</t>
+          <t>23:18</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>31.6%</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>32:45</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>54:29</t>
+          <t>24:30</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>12.8%</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>36:43</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AN42" t="n">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
@@ -5860,10 +5860,10 @@
         <v>13</v>
       </c>
       <c r="T43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>58:59</t>
+          <t>29:00</t>
         </is>
       </c>
       <c r="AN43" t="n">
@@ -5976,12 +5976,12 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>5.5%</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AN45" t="n">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>36:41</t>
+          <t>26:42</t>
         </is>
       </c>
       <c r="AN46" t="n">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
@@ -6784,16 +6784,16 @@
         <v>84</v>
       </c>
       <c r="T48" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
         <v>24</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_393_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_393_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,10 +1335,10 @@
         <v>20</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1531,10 +1531,10 @@
         <v>17</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>6</v>
@@ -2315,16 +2315,16 @@
         <v>31</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X22" t="n">
         <v>10</v>
@@ -3494,13 +3494,13 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
         <v>4</v>
@@ -3827,16 +3827,16 @@
         <v>105</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X30" t="n">
         <v>29</v>
@@ -4292,7 +4292,7 @@
         <v>16</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -4684,16 +4684,16 @@
         <v>13</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X37" t="n">
         <v>9</v>
@@ -5079,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -5670,10 +5670,10 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" t="n">
         <v>1</v>
@@ -5860,10 +5860,10 @@
         <v>13</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6059,7 +6059,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>84</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X48" t="n">
         <v>24</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_393_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_393_EL.xlsx
@@ -674,10 +674,10 @@
         <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -692,20 +692,20 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>78.38</t>
+          <t>57.89</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="O3" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="P3" t="n">
         <v>7</v>
@@ -854,17 +854,17 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
         <v>5</v>
       </c>
       <c r="W3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>82.76</t>
+          <t>77.27</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1543,14 +1543,14 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -1739,14 +1739,14 @@
         <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -2327,14 +2327,14 @@
         <v>3</v>
       </c>
       <c r="X22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -2360,25 +2360,25 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK22" t="n">
         <v>3</v>
       </c>
-      <c r="AK22" t="n">
-        <v>4</v>
-      </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -2523,14 +2523,14 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -3503,14 +3503,14 @@
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>5</v>
       </c>
       <c r="X30" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="Y30" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3872,25 +3872,25 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4500,14 +4500,14 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -4696,14 +4696,14 @@
         <v>3</v>
       </c>
       <c r="X37" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -4732,7 +4732,7 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y43" t="n">
         <v>6</v>
       </c>
-      <c r="Y43" t="n">
-        <v>9</v>
-      </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6796,14 +6796,14 @@
         <v>4</v>
       </c>
       <c r="X48" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="Y48" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6832,22 +6832,22 @@
         <v>2</v>
       </c>
       <c r="AH48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AJ48" t="n">
         <v>5</v>
       </c>
       <c r="AK48" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
